--- a/analise_eua/semicondutores/amd/amd_10q.xlsx
+++ b/analise_eua/semicondutores/amd/amd_10q.xlsx
@@ -433,65 +433,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44828</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44464</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44100</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
     </row>
@@ -502,60 +505,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>5086</v>
+      </c>
+      <c r="C2" t="n">
         <v>5585</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>4808</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>4442</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>6049</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>3897</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4113</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>4190</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>3561</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>3841</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>3825</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>3398</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>4964</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>4740</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2440</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>2623</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>1763</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>1296</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>1775</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1330</v>
       </c>
     </row>
@@ -566,60 +572,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>8025</v>
+      </c>
+      <c r="C3" t="n">
         <v>6762</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>2435</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1425</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1261</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>647</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1227</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1845</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2224</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2444</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>2114</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2193</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1028</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1792</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1168</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>1170</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1353</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>475</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>55</v>
       </c>
     </row>
@@ -630,60 +639,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>7281</v>
+      </c>
+      <c r="C4" t="n">
         <v>6035</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>6201</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>5115</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5443</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>7241</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>5749</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5038</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5054</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>4312</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4040</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>4336</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>4050</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>3677</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>2224</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>2020</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>2178</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>2134</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1789</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1691</v>
       </c>
     </row>
@@ -694,60 +706,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>8468</v>
+      </c>
+      <c r="C5" t="n">
         <v>8045</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>7313</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>6677</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>6416</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>5374</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4991</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4652</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>4445</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>4567</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4235</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>3369</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2648</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>2431</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1902</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1765</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1653</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1292</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>1324</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1056</v>
       </c>
     </row>
@@ -758,60 +773,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>2662</v>
+      </c>
+      <c r="C6" t="n">
         <v>2201</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>2253</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>2534</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2426</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1547</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1361</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1328</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>1403</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>1339</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>1442</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1120</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>769</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>725</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>249</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>234</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>243</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>299</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>211</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>241</v>
       </c>
     </row>
@@ -822,60 +840,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>31522</v>
+      </c>
+      <c r="C7" t="n">
         <v>28628</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>27000</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>24519</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>21595</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>18735</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>17465</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>17084</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>16688</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>16505</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>15658</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>14420</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>13462</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>13369</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>7988</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>7818</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>7197</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>5500</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>5109</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>4390</v>
       </c>
     </row>
@@ -886,60 +907,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>3439</v>
+      </c>
+      <c r="C8" t="n">
         <v>2723</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>2205</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>2128</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1921</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1669</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1666</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1624</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1566</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>1541</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1500</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1486</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1441</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1406</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>717</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>671</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>681</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>595</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>585</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>540</v>
       </c>
     </row>
@@ -950,46 +974,46 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>25470</v>
+      </c>
+      <c r="C9" t="n">
         <v>25344</v>
-      </c>
-      <c r="C9" t="n">
-        <v>25083</v>
       </c>
       <c r="D9" t="n">
         <v>25083</v>
       </c>
       <c r="E9" t="n">
-        <v>24839</v>
+        <v>25083</v>
       </c>
       <c r="F9" t="n">
         <v>24839</v>
       </c>
       <c r="G9" t="n">
-        <v>24262</v>
+        <v>24839</v>
       </c>
       <c r="H9" t="n">
         <v>24262</v>
       </c>
       <c r="I9" t="n">
+        <v>24262</v>
+      </c>
+      <c r="J9" t="n">
         <v>24186</v>
-      </c>
-      <c r="J9" t="n">
-        <v>24177</v>
       </c>
       <c r="K9" t="n">
         <v>24177</v>
       </c>
       <c r="L9" t="n">
+        <v>24177</v>
+      </c>
+      <c r="M9" t="n">
         <v>24187</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>24193</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>23083</v>
-      </c>
-      <c r="O9" t="n">
-        <v>289</v>
       </c>
       <c r="P9" t="n">
         <v>289</v>
@@ -1006,6 +1030,9 @@
       <c r="T9" t="n">
         <v>289</v>
       </c>
+      <c r="U9" t="n">
+        <v>289</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1014,47 +1041,47 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>15635</v>
+      </c>
+      <c r="C10" t="n">
         <v>16154</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>17250</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>17812</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>18363</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>19572</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>20138</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>20741</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>21950</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>22598</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>23291</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>25162</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>26159</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>26832</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1068,6 +1095,9 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1078,37 +1108,37 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>494</v>
+      </c>
+      <c r="C11" t="n">
         <v>476</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>633</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>860</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>845</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1183</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>617</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>433</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>76</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>68</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>67</v>
-      </c>
-      <c r="L11" t="n">
-        <v>32</v>
       </c>
       <c r="M11" t="n">
         <v>32</v>
@@ -1117,21 +1147,24 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
+        <v>32</v>
+      </c>
+      <c r="P11" t="n">
         <v>1036</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>1090</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>1162</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1142,60 +1175,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>7904</v>
+      </c>
+      <c r="C12" t="n">
         <v>6317</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>4720</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>4418</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>3987</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>2854</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>2990</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3013</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>2560</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>2527</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>2410</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1954</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1657</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>1705</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>770</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>509</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>412</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>364</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>326</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>366</v>
       </c>
     </row>
@@ -1206,60 +1242,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>84464</v>
+      </c>
+      <c r="C13" t="n">
         <v>79642</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>76891</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>74820</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>71550</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>69636</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>67886</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>67895</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>67626</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>67967</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>67634</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>67811</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>67502</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>66915</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>11153</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>10691</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10047</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>7023</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>6583</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>5864</v>
       </c>
     </row>
@@ -1270,60 +1309,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>5359</v>
+      </c>
+      <c r="C14" t="n">
         <v>2997</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>3483</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>3080</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>2206</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>2530</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1699</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1418</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>2245</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>2779</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>2518</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2337</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1518</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1476</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1048</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>836</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>949</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>752</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>802</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>653</v>
       </c>
     </row>
@@ -1334,20 +1376,20 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>5546</v>
+      </c>
+      <c r="C15" t="n">
         <v>5785</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>5112</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>4479</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>3876</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
@@ -1388,6 +1430,9 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1398,60 +1443,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>301</v>
+      </c>
+      <c r="C16" t="n">
         <v>850</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>324</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>316</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>674</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>389</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>447</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>424</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>929</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>756</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>539</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>359</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>258</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>518</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>120</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>109</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>96</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>72</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>68</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>75</v>
       </c>
     </row>
@@ -1462,60 +1510,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>12081</v>
+      </c>
+      <c r="C17" t="n">
         <v>10506</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>11700</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>9843</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>7703</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>7500</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>6195</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>6474</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>7627</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>7572</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6577</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>6691</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>5523</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>5581</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>3564</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>2892</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>2864</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>2417</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>2434</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>1985</v>
       </c>
     </row>
@@ -1526,60 +1577,63 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>2351</v>
+      </c>
+      <c r="C18" t="n">
         <v>2350</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>2347</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>3218</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>3217</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1720</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1719</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1718</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1715</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>1714</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>2467</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2466</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>2465</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>1475</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>313</v>
       </c>
       <c r="Q18" t="n">
         <v>313</v>
       </c>
       <c r="R18" t="n">
+        <v>313</v>
+      </c>
+      <c r="S18" t="n">
         <v>373</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>490</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>488</v>
       </c>
     </row>
@@ -1590,60 +1644,63 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C19" t="n">
         <v>647</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>650</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>668</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>567</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>518</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>526</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>530</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>395</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>393</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>381</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>424</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>422</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>370</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>269</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>240</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>238</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>205</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>204</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>211</v>
       </c>
     </row>
@@ -1654,47 +1711,47 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>300</v>
+      </c>
+      <c r="C20" t="n">
         <v>307</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>326</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>341</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>343</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>1162</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>1192</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>1199</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>1152</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>1365</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>1641</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2078</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>2805</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3109</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
@@ -1708,6 +1765,9 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1718,60 +1778,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>1458</v>
+      </c>
+      <c r="C21" t="n">
         <v>1370</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>1078</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>1085</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1839</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>1751</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>1716</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>1776</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>1767</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>1787</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>1874</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>1610</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1118</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>1047</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>183</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>181</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>155</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>161</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>150</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>143</v>
       </c>
     </row>
@@ -1782,7 +1845,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
         <v>17</v>
@@ -1806,7 +1869,7 @@
         <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
         <v>16</v>
@@ -1821,7 +1884,7 @@
         <v>16</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
         <v>12</v>
@@ -1838,6 +1901,9 @@
       <c r="T22" t="n">
         <v>12</v>
       </c>
+      <c r="U22" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1846,60 +1912,63 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>61373</v>
+      </c>
+      <c r="C23" t="n">
         <v>63856</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>62657</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>62228</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>61730</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>60896</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>60542</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>60053</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>59182</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>58825</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>58331</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>57581</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>57297</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>56925</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>10905</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>10795</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>10658</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>10362</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>10127</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>10026</v>
       </c>
     </row>
@@ -1910,62 +1979,65 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
         <v>-7421</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>-7059</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>-6535</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-6899</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-5812</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-5103</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-4690</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-4235</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-3430</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-3362</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-2815</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>-1893</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>-941</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>-1356</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>-401</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>-141</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>-126</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-54</v>
       </c>
       <c r="T24" t="n">
         <v>-54</v>
       </c>
+      <c r="U24" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1974,60 +2046,63 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>5909</v>
+      </c>
+      <c r="C25" t="n">
         <v>8082</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>5188</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>3945</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>3073</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>1882</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>1111</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>846</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>56</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-243</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-270</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-152</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-218</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-665</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>-2425</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>-3348</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>-4058</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>-6386</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-6776</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>-6933</v>
       </c>
     </row>
@@ -2038,60 +2113,63 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>-74</v>
+      </c>
+      <c r="C26" t="n">
         <v>-72</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>-13</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>-40</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-29</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-28</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>-50</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>-32</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>-21</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>-88</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-33</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>-2</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>7</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>6</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>5</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>-4</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-14</v>
       </c>
     </row>
@@ -2102,60 +2180,63 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>67224</v>
+      </c>
+      <c r="C27" t="n">
         <v>64462</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>60790</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>59665</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>57881</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>56985</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>56538</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>56198</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>54970</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>55136</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>54694</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>54542</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>55169</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>55333</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>7136</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>7065</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>6477</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>3867</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>3305</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>3037</v>
       </c>
     </row>
@@ -2169,14 +2250,14 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
         <v>3990</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>4326</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
@@ -2220,6 +2301,9 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2233,14 +2317,14 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
         <v>1908</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>1968</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
@@ -2284,6 +2368,9 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2294,40 +2381,40 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
         <v>874</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>873</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
       <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>947</v>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>750</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>752</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>753</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>312</v>
@@ -2336,7 +2423,7 @@
         <v>312</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2345,9 +2432,12 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
         <v>200</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2370,48 +2460,51 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
         <v>29</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>24</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>31</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
       <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="n">
         <v>4</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>3</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>4</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>5</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>7</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>4</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>10</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2434,48 +2527,51 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
         <v>647</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>635</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>632</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>507</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>461</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>447</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>490</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>482</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>416</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>284</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>247</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>241</v>
-      </c>
-      <c r="R32" t="n">
-        <v>215</v>
       </c>
       <c r="S32" t="n">
         <v>215</v>
       </c>
       <c r="T32" t="n">
+        <v>215</v>
+      </c>
+      <c r="U32" t="n">
         <v>221</v>
       </c>
     </row>
@@ -2498,48 +2594,51 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
         <v>137</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>113</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>106</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>93</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>90</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>84</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>80</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>76</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>72</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>69</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>67</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>65</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>60</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>59</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>58</v>
       </c>
     </row>
@@ -2562,48 +2661,51 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
         <v>461</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>420</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>438</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>325</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>397</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>361</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>205</v>
-      </c>
-      <c r="O34" t="n">
-        <v>36</v>
       </c>
       <c r="P34" t="n">
         <v>36</v>
       </c>
       <c r="Q34" t="n">
+        <v>36</v>
+      </c>
+      <c r="R34" t="n">
         <v>40</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>115</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>192</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>187</v>
       </c>
     </row>
@@ -2626,48 +2728,51 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
         <v>4120</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>3629</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>3444</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>3376</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>2971</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>3167</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>3598</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>3074</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>3070</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>2048</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>1911</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>1779</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>1478</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>1172</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>1070</v>
       </c>
     </row>
@@ -2682,65 +2787,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44828</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44464</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44100</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
     </row>
@@ -2751,60 +2859,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>11536</v>
+      </c>
+      <c r="C2" t="n">
         <v>10253</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>9246</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>7685</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>7438</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>6819</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>5835</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>5473</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5800</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5359</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>5353</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>5565</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>6550</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>5887</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>4313</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3850</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>3445</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>2801</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>1932</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1786</v>
       </c>
     </row>
@@ -2815,60 +2926,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5333</v>
+      </c>
+      <c r="C3" t="n">
         <v>4837</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>4466</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>4626</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>3702</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>3400</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2971</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2913</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>3053</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2916</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>2994</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3211</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3522</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>3069</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>2227</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2020</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1858</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1571</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1084</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>968</v>
       </c>
     </row>
@@ -2879,60 +2993,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>6203</v>
+      </c>
+      <c r="C4" t="n">
         <v>5416</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>4780</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>3059</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3736</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>3419</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2864</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2560</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2747</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>2443</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>2359</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>2354</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>3028</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>2818</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>2086</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1830</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1587</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1230</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>848</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>818</v>
       </c>
     </row>
@@ -2943,60 +3060,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2528</v>
+      </c>
+      <c r="C5" t="n">
         <v>2397</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>2139</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1894</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1728</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1636</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1583</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1525</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1507</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>1443</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1411</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1279</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1300</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>1060</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>765</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>659</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>610</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>508</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>460</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>442</v>
       </c>
     </row>
@@ -3007,60 +3127,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1401</v>
+      </c>
+      <c r="C6" t="n">
         <v>1253</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1069</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>991</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>886</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>721</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>650</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>620</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>576</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>547</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>585</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>557</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>592</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>597</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>376</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>341</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>319</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>273</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>215</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>199</v>
       </c>
     </row>
@@ -3071,47 +3194,47 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>284</v>
+      </c>
+      <c r="C7" t="n">
         <v>290</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>302</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>308</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>316</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>352</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>372</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>392</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>450</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>481</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>518</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>590</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>616</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>293</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -3125,6 +3248,9 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3135,20 +3261,20 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4213</v>
+      </c>
+      <c r="C8" t="n">
         <v>3940</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>3510</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>3193</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2930</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
@@ -3189,6 +3315,9 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3199,60 +3328,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C9" t="n">
         <v>1476</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1270</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-134</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>806</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>724</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>269</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>36</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>224</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-20</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-145</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-64</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>526</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>951</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>948</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>831</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>662</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>449</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>173</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>177</v>
       </c>
     </row>
@@ -3269,54 +3401,57 @@
         <v>-37</v>
       </c>
       <c r="D10" t="n">
+        <v>-37</v>
+      </c>
+      <c r="E10" t="n">
         <v>-38</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-20</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-23</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-25</v>
       </c>
       <c r="H10" t="n">
         <v>-25</v>
       </c>
       <c r="I10" t="n">
+        <v>-25</v>
+      </c>
+      <c r="J10" t="n">
         <v>-26</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-28</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-25</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-31</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-25</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-13</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-7</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-10</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-9</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-11</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-14</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-13</v>
       </c>
     </row>
@@ -3327,60 +3462,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>598</v>
+      </c>
+      <c r="C11" t="n">
         <v>165</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>82</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>98</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>39</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>36</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>55</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>53</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>59</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>46</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>43</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>22</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-4</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-42</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>62</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>-11</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>-37</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3391,60 +3529,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2551</v>
+      </c>
+      <c r="C12" t="n">
         <v>1604</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>1315</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-74</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>825</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>737</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>299</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>64</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>257</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-2</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-127</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-73</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>497</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>896</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1003</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>821</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>642</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>401</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>160</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>168</v>
       </c>
     </row>
@@ -3455,60 +3596,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>252</v>
+      </c>
+      <c r="C13" t="n">
         <v>238</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>153</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-834</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>123</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-27</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>41</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-52</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-39</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-23</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>13</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-135</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>54</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>113</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>82</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>113</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>89</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>12</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>4</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3522,13 +3666,13 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>7</v>
       </c>
       <c r="F14" t="n">
         <v>7</v>
@@ -3540,25 +3684,25 @@
         <v>7</v>
       </c>
       <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4</v>
       </c>
       <c r="M14" t="n">
         <v>4</v>
       </c>
       <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
         <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -3567,12 +3711,15 @@
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3583,60 +3730,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>2297</v>
+      </c>
+      <c r="C15" t="n">
         <v>1383</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>1243</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>872</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>709</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>771</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>265</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>123</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>299</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>27</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-139</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>66</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>447</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>786</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>923</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>710</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>555</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>390</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>157</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>162</v>
       </c>
     </row>
@@ -3647,60 +3797,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C16" t="n">
         <v>0.85</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>0.76</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>0.54</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>0.44</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.48</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.16</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.08</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0.18</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>0.02</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-0.09</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.04</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0.28</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>0.76</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>0.58</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>0.46</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>0.33</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>0.13</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>0.14</v>
       </c>
     </row>
@@ -3711,14 +3864,14 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="C17" t="n">
         <v>0.83</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>0.71</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
@@ -3765,199 +3918,211 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Basic</t>
+          <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1631</v>
+        <v>1.38</v>
       </c>
       <c r="C18" t="n">
-        <v>1626</v>
+        <v>0.01</v>
       </c>
       <c r="D18" t="n">
-        <v>1623</v>
+        <v>0.75</v>
       </c>
       <c r="E18" t="n">
-        <v>1620</v>
+        <v>0.54</v>
       </c>
       <c r="F18" t="n">
-        <v>1620</v>
+        <v>0.44</v>
       </c>
       <c r="G18" t="n">
-        <v>1618</v>
+        <v>0.47</v>
       </c>
       <c r="H18" t="n">
-        <v>1617</v>
+        <v>0.16</v>
       </c>
       <c r="I18" t="n">
-        <v>1616</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1612</v>
+        <v>0.18</v>
       </c>
       <c r="K18" t="n">
-        <v>1611</v>
+        <v>0.02</v>
       </c>
       <c r="L18" t="n">
-        <v>1615</v>
+        <v>-0.09</v>
       </c>
       <c r="M18" t="n">
-        <v>1618</v>
+        <v>0.04</v>
       </c>
       <c r="N18" t="n">
-        <v>1393</v>
+        <v>0.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1214</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1216</v>
+        <v>0.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1213</v>
+        <v>0.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1184</v>
+        <v>0.45</v>
       </c>
       <c r="S18" t="n">
-        <v>1174</v>
+        <v>0.32</v>
       </c>
       <c r="T18" t="n">
-        <v>1170</v>
+        <v>0.13</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Diluted</t>
+          <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1650</v>
+        <v>1632</v>
       </c>
       <c r="C19" t="n">
-        <v>1641</v>
+        <v>1631</v>
       </c>
       <c r="D19" t="n">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="E19" t="n">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="F19" t="n">
-        <v>1636</v>
+        <v>1620</v>
       </c>
       <c r="G19" t="n">
-        <v>1637</v>
+        <v>1620</v>
       </c>
       <c r="H19" t="n">
-        <v>1639</v>
+        <v>1618</v>
       </c>
       <c r="I19" t="n">
-        <v>1629</v>
+        <v>1617</v>
       </c>
       <c r="J19" t="n">
-        <v>1627</v>
+        <v>1616</v>
       </c>
       <c r="K19" t="n">
+        <v>1612</v>
+      </c>
+      <c r="L19" t="n">
         <v>1611</v>
       </c>
-      <c r="L19" t="n">
-        <v>1625</v>
-      </c>
       <c r="M19" t="n">
-        <v>1632</v>
+        <v>1615</v>
       </c>
       <c r="N19" t="n">
-        <v>1410</v>
+        <v>1618</v>
       </c>
       <c r="O19" t="n">
-        <v>1230</v>
+        <v>1393</v>
       </c>
       <c r="P19" t="n">
-        <v>1232</v>
+        <v>1214</v>
       </c>
       <c r="Q19" t="n">
-        <v>1231</v>
+        <v>1216</v>
       </c>
       <c r="R19" t="n">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="S19" t="n">
-        <v>1227</v>
+        <v>1184</v>
       </c>
       <c r="T19" t="n">
-        <v>1224</v>
+        <v>1174</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1170</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Diluted</t>
+          <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.01</v>
+        <v>1659</v>
       </c>
       <c r="C20" t="n">
-        <v>0.75</v>
+        <v>1650</v>
       </c>
       <c r="D20" t="n">
-        <v>0.54</v>
+        <v>1641</v>
       </c>
       <c r="E20" t="n">
-        <v>0.44</v>
+        <v>1630</v>
       </c>
       <c r="F20" t="n">
-        <v>0.47</v>
+        <v>1626</v>
       </c>
       <c r="G20" t="n">
-        <v>0.16</v>
+        <v>1636</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07000000000000001</v>
+        <v>1637</v>
       </c>
       <c r="I20" t="n">
-        <v>0.18</v>
+        <v>1639</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02</v>
+        <v>1629</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.09</v>
+        <v>1627</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04</v>
+        <v>1611</v>
       </c>
       <c r="M20" t="n">
-        <v>0.27</v>
+        <v>1625</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5600000000000001</v>
+        <v>1632</v>
       </c>
       <c r="O20" t="n">
-        <v>0.75</v>
+        <v>1410</v>
       </c>
       <c r="P20" t="n">
-        <v>0.58</v>
+        <v>1230</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.45</v>
+        <v>1232</v>
       </c>
       <c r="R20" t="n">
-        <v>0.32</v>
+        <v>1231</v>
       </c>
       <c r="S20" t="n">
-        <v>0.13</v>
+        <v>1215</v>
       </c>
       <c r="T20" t="n">
-        <v>0.14</v>
+        <v>1227</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1224</v>
       </c>
     </row>
     <row r="21">
@@ -3979,48 +4144,51 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>-14</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-10</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-13</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-10</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-8</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-10</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-8</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-6</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-83</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-3</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>-1</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>-4</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4035,65 +4203,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46109</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45927</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45836</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45745</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45563</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45472</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45381</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45108</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45017</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44828</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44737</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44646</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44464</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44373</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44282</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44100</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44009</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43918</v>
       </c>
     </row>
@@ -4104,60 +4275,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>3680</v>
+      </c>
+      <c r="C2" t="n">
         <v>1383</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>2824</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1581</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>709</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1159</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>388</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>123</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>187</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-112</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-139</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1299</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1233</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>786</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2188</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>1265</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>555</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>709</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>319</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>162</v>
       </c>
     </row>
@@ -4168,60 +4342,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>427</v>
+      </c>
+      <c r="C3" t="n">
         <v>206</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>556</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>364</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>175</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2309</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1553</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>784</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2654</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1831</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>982</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2954</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1789</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>609</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>289</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>192</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>95</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>222</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>140</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4232,20 +4409,20 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="C4" t="n">
         <v>551</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1697</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1135</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>567</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -4286,6 +4463,9 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4296,60 +4476,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>990</v>
+      </c>
+      <c r="C5" t="n">
         <v>487</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>1152</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>733</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>364</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1068</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>717</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>371</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1010</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>657</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>309</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>766</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>491</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>199</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>267</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>168</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>85</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>195</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>119</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>59</v>
       </c>
     </row>
@@ -4360,60 +4543,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-106</v>
+      </c>
+      <c r="C6" t="n">
         <v>-79</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>18</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-200</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-167</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-863</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-256</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-66</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-800</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-582</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-308</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-1328</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>-618</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>-342</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>201</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>145</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>73</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4424,11 +4610,11 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>-549</v>
+      </c>
+      <c r="C7" t="n">
         <v>-66</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
@@ -4478,6 +4664,9 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4488,60 +4677,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>61</v>
+      </c>
+      <c r="C8" t="n">
         <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>29</v>
       </c>
       <c r="D8" t="n">
         <v>29</v>
       </c>
       <c r="E8" t="n">
+        <v>29</v>
+      </c>
+      <c r="F8" t="n">
         <v>39</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-50</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>-37</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>-22</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-43</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-20</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>-2</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>-9</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>-4</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>-2</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-6</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>-4</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>-3</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>12</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4552,60 +4744,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-966</v>
+      </c>
+      <c r="C9" t="n">
         <v>280</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-7</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>1078</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>748</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-1862</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-373</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>338</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>-929</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-186</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>86</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-1301</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-1016</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-672</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>-158</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>46</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-112</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-287</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>64</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>168</v>
       </c>
     </row>
@@ -4616,60 +4811,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-548</v>
+      </c>
+      <c r="C10" t="n">
         <v>-125</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-1579</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-943</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-682</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-1096</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-710</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-368</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-674</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-796</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-464</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-997</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-274</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-26</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-504</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-366</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-254</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-310</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-342</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-74</v>
       </c>
     </row>
@@ -4680,60 +4878,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-991</v>
+      </c>
+      <c r="C11" t="n">
         <v>-308</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-259</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-377</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>-237</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>-250</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-234</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-322</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>-380</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>-237</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-191</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-825</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>-237</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-260</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>-284</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>-55</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>33</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>-172</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-12</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-31</v>
       </c>
     </row>
@@ -4744,60 +4945,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2170</v>
+      </c>
+      <c r="C12" t="n">
         <v>-104</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>998</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>547</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-289</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>476</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-356</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-636</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-238</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>309</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>73</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>811</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>28</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>526</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>346</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>466</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>121</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>-161</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-429</v>
       </c>
     </row>
@@ -4808,60 +5012,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>61</v>
+      </c>
+      <c r="C13" t="n">
         <v>713</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-145</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-589</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-288</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>626</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>263</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>175</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>550</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>91</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>218</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>994</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>71</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>412</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>199</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>90</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-41</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4872,60 +5079,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>5321</v>
+      </c>
+      <c r="C14" t="n">
         <v>2955</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>5109</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>2950</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>939</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1742</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1114</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>521</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1286</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>865</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>486</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2998</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>2033</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>995</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>2699</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1850</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>898</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>517</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>178</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>-65</v>
       </c>
     </row>
@@ -4936,60 +5146,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>-1197</v>
+      </c>
+      <c r="C15" t="n">
         <v>-389</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>-752</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>-494</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>-212</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>-428</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>-296</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-142</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-407</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-283</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-158</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>-326</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>-203</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>-71</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-215</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>-130</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>-66</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>-220</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-146</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -5000,62 +5213,65 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>-4555</v>
+      </c>
+      <c r="C16" t="n">
         <v>-2545</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>-2110</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>-796</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-304</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-707</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>-565</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>-433</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-3312</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-2816</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-1703</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>-2399</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-620</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-100</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>-1901</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>-1130</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>-858</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>-530</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-55</v>
       </c>
       <c r="T16" t="n">
         <v>-55</v>
       </c>
+      <c r="U16" t="n">
+        <v>-55</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -5064,60 +5280,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>1267</v>
+      </c>
+      <c r="C17" t="n">
         <v>652</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>982</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>683</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>365</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>1351</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>1202</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>441</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1917</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>1171</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>473</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2864</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2249</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>964</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1428</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>655</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>200</v>
-      </c>
-      <c r="R17" t="n">
-        <v>92</v>
       </c>
       <c r="S17" t="n">
         <v>92</v>
       </c>
       <c r="T17" t="n">
+        <v>92</v>
+      </c>
+      <c r="U17" t="n">
         <v>37</v>
       </c>
     </row>
@@ -5128,38 +5347,38 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>286</v>
+      </c>
+      <c r="C18" t="n">
         <v>126</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>66</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>48</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>33</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>591</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
       </c>
       <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
         <v>248</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>145</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -5182,6 +5401,9 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5192,20 +5414,20 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>-844</v>
+      </c>
+      <c r="C19" t="n">
         <v>-409</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>-432</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>-358</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>-239</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
@@ -5246,90 +5468,96 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Investing Activities</t>
+          <t>amd_PaymentsToAcquirePropertyPlantAndEquipmentFromDiscontinuedOperation</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-2565</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-3992</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-2655</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-357</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-135</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-1573</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-1675</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-1237</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>932</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2230</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3158</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-686</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-603</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-722</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-658</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-109</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-73</v>
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Long-term Debt</t>
+          <t>Payments for (Proceeds from) Businesses and Interest in Affiliates</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-243</v>
       </c>
       <c r="C21" t="n">
-        <v>2441</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2441</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1494</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -5374,123 +5602,129 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Proceeds, Issuance of Shares, Share-based Payment Arrangement, Including Option Exercised</t>
+          <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>-5415</v>
       </c>
       <c r="C22" t="n">
-        <v>169</v>
+        <v>-2565</v>
       </c>
       <c r="D22" t="n">
-        <v>159</v>
+        <v>-3992</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>-2655</v>
       </c>
       <c r="F22" t="n">
-        <v>152</v>
+        <v>-357</v>
       </c>
       <c r="G22" t="n">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>251</v>
       </c>
       <c r="I22" t="n">
-        <v>148</v>
+        <v>-135</v>
       </c>
       <c r="J22" t="n">
-        <v>144</v>
+        <v>-1573</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>-1675</v>
       </c>
       <c r="L22" t="n">
-        <v>79</v>
+        <v>-1237</v>
       </c>
       <c r="M22" t="n">
-        <v>78</v>
+        <v>932</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2230</v>
       </c>
       <c r="O22" t="n">
-        <v>55</v>
+        <v>3158</v>
       </c>
       <c r="P22" t="n">
-        <v>51</v>
+        <v>-686</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>-603</v>
       </c>
       <c r="R22" t="n">
-        <v>45</v>
+        <v>-722</v>
       </c>
       <c r="S22" t="n">
-        <v>42</v>
+        <v>-658</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>-109</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Payments for Repurchase of Common Stock</t>
+          <t>Proceeds from Issuance of Long-term Debt</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-221</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>-1316</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-1227</v>
+        <v>2441</v>
       </c>
       <c r="E23" t="n">
-        <v>-749</v>
+        <v>2441</v>
       </c>
       <c r="F23" t="n">
-        <v>-606</v>
+        <v>1494</v>
       </c>
       <c r="G23" t="n">
-        <v>-356</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-752</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-241</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-241</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-3452</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-2835</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1914</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-1004</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-256</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -5502,312 +5736,327 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
+          <t>Repayments of Commercial Paper</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-134</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>-447</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-76</v>
+        <v>-950</v>
       </c>
       <c r="E24" t="n">
-        <v>-30</v>
+        <v>-950</v>
       </c>
       <c r="F24" t="n">
-        <v>-686</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-226</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-129</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>-382</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-87</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-371</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-66</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>-35</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-219</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Proceeds, Issuance of Shares, Share-based Payment Arrangement, Including Option Exercised</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-350</v>
+        <v>205</v>
       </c>
       <c r="C25" t="n">
-        <v>-103</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>347</v>
+        <v>169</v>
       </c>
       <c r="E25" t="n">
-        <v>1666</v>
+        <v>159</v>
       </c>
       <c r="F25" t="n">
-        <v>-1891</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>-1185</v>
+        <v>152</v>
       </c>
       <c r="H25" t="n">
-        <v>-129</v>
+        <v>148</v>
       </c>
       <c r="I25" t="n">
-        <v>-987</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>-184</v>
+        <v>148</v>
       </c>
       <c r="K25" t="n">
-        <v>-259</v>
+        <v>144</v>
       </c>
       <c r="L25" t="n">
-        <v>-3067</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>-1834</v>
+        <v>79</v>
       </c>
       <c r="N25" t="n">
-        <v>-1948</v>
+        <v>78</v>
       </c>
       <c r="O25" t="n">
-        <v>-1168</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>-219</v>
+        <v>55</v>
       </c>
       <c r="Q25" t="n">
-        <v>-8</v>
+        <v>51</v>
       </c>
       <c r="R25" t="n">
-        <v>-29</v>
+        <v>2</v>
       </c>
       <c r="S25" t="n">
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>-221</v>
       </c>
       <c r="C26" t="n">
-        <v>1014</v>
+        <v>-221</v>
       </c>
       <c r="D26" t="n">
-        <v>642</v>
+        <v>-1316</v>
       </c>
       <c r="E26" t="n">
-        <v>2248</v>
+        <v>-1227</v>
       </c>
       <c r="F26" t="n">
-        <v>-36</v>
+        <v>-749</v>
       </c>
       <c r="G26" t="n">
-        <v>180</v>
+        <v>-606</v>
       </c>
       <c r="H26" t="n">
-        <v>257</v>
+        <v>-356</v>
       </c>
       <c r="I26" t="n">
-        <v>-1274</v>
+        <v>-4</v>
       </c>
       <c r="J26" t="n">
-        <v>-994</v>
+        <v>-752</v>
       </c>
       <c r="K26" t="n">
-        <v>-1010</v>
+        <v>-241</v>
       </c>
       <c r="L26" t="n">
-        <v>863</v>
+        <v>-241</v>
       </c>
       <c r="M26" t="n">
-        <v>2429</v>
+        <v>-3452</v>
       </c>
       <c r="N26" t="n">
-        <v>2205</v>
+        <v>-2835</v>
       </c>
       <c r="O26" t="n">
-        <v>845</v>
+        <v>-1914</v>
       </c>
       <c r="P26" t="n">
-        <v>1028</v>
+        <v>-1004</v>
       </c>
       <c r="Q26" t="n">
-        <v>168</v>
+        <v>-256</v>
       </c>
       <c r="R26" t="n">
-        <v>-170</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-136</v>
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Including Disposal Group and Discontinued Operations</t>
+          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5596</v>
+        <v>-341</v>
       </c>
       <c r="C27" t="n">
-        <v>4825</v>
+        <v>-134</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-447</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-76</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-686</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-226</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-129</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-382</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>-87</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>-371</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-219</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Income Taxes Paid, Net</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>-8</v>
       </c>
       <c r="C28" t="n">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1011</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>311</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>87</v>
+        <v>-1</v>
       </c>
       <c r="I28" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>544</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -5819,154 +6068,163 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Capital Expenditures Incurred but Not yet Paid</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>329</v>
+        <v>-365</v>
       </c>
       <c r="C29" t="n">
-        <v>153</v>
+        <v>-350</v>
       </c>
       <c r="D29" t="n">
-        <v>333</v>
+        <v>-103</v>
       </c>
       <c r="E29" t="n">
-        <v>147</v>
+        <v>347</v>
       </c>
       <c r="F29" t="n">
-        <v>99</v>
+        <v>1666</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>-1891</v>
       </c>
       <c r="H29" t="n">
-        <v>102</v>
+        <v>-1185</v>
       </c>
       <c r="I29" t="n">
-        <v>113</v>
+        <v>-129</v>
       </c>
       <c r="J29" t="n">
-        <v>99</v>
+        <v>-987</v>
       </c>
       <c r="K29" t="n">
-        <v>69</v>
+        <v>-184</v>
       </c>
       <c r="L29" t="n">
-        <v>122</v>
+        <v>-259</v>
       </c>
       <c r="M29" t="n">
-        <v>149</v>
+        <v>-3067</v>
       </c>
       <c r="N29" t="n">
-        <v>67</v>
+        <v>-1834</v>
       </c>
       <c r="O29" t="n">
-        <v>74</v>
+        <v>-1948</v>
       </c>
       <c r="P29" t="n">
-        <v>41</v>
+        <v>-1168</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>-219</v>
       </c>
       <c r="R29" t="n">
-        <v>36</v>
+        <v>-8</v>
       </c>
       <c r="S29" t="n">
-        <v>52</v>
+        <v>-29</v>
       </c>
       <c r="T29" t="n">
-        <v>99</v>
+        <v>240</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Release Of Reserves For Tax Liabilities</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-459</v>
       </c>
       <c r="C30" t="n">
-        <v>-853</v>
+        <v>40</v>
       </c>
       <c r="D30" t="n">
-        <v>-853</v>
+        <v>1014</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>642</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2248</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-1274</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>-994</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-1010</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>863</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2429</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2205</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1028</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>-170</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>309</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-136</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>amd_InventoryLossAtRecoveryFromContractManufacturer</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Including Disposal Group and Discontinued Operations</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>5097</v>
       </c>
       <c r="C31" t="n">
-        <v>-67</v>
+        <v>5596</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>4825</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -6014,62 +6272,65 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Payments for (Proceeds from) Other Investing Activities</t>
+          <t>Income Taxes Paid, Net</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>777</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>760</v>
       </c>
       <c r="F32" t="n">
-        <v>-129</v>
+        <v>128</v>
       </c>
       <c r="G32" t="n">
-        <v>-92</v>
+        <v>1011</v>
       </c>
       <c r="H32" t="n">
-        <v>-3</v>
+        <v>311</v>
       </c>
       <c r="I32" t="n">
-        <v>-5</v>
+        <v>87</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="L32" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-4</v>
+        <v>584</v>
       </c>
       <c r="N32" t="n">
-        <v>-1</v>
+        <v>544</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6078,81 +6339,87 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Commercial Paper</t>
+          <t>Capital Expenditures Incurred but Not yet Paid</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="C33" t="n">
-        <v>-950</v>
+        <v>329</v>
       </c>
       <c r="D33" t="n">
-        <v>-950</v>
+        <v>153</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>52</v>
+      </c>
+      <c r="U33" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments for) Other Financing Activities</t>
+          <t>Right-of-Use Asset Obtained in Exchange for Operating Lease Liability</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>514</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -6164,55 +6431,58 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>95</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="N34" t="n">
-        <v>-1</v>
+        <v>87</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="R34" t="n">
-        <v>-1</v>
+        <v>58</v>
       </c>
       <c r="S34" t="n">
-        <v>-2</v>
+        <v>40</v>
       </c>
       <c r="T34" t="n">
-        <v>-1</v>
+        <v>30</v>
+      </c>
+      <c r="U34" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Disposal Group, Including Discontinued Operations</t>
+          <t>Release Of Reserves For Tax Liabilities</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6222,10 +6492,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-853</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>-853</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -6270,13 +6540,16 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>amd_InventoryLossAtRecoveryFromContractManufacturer</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6286,61 +6559,64 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3811</v>
+        <v>-67</v>
       </c>
       <c r="E36" t="n">
-        <v>3811</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>3933</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>3933</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3933</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4835</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>4835</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>4835</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>2535</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2535</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2535</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1595</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1595</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1595</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1470</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1470</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1470</v>
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Commercial Paper</t>
+          <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6353,58 +6629,61 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-129</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-92</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Operating Lease, Right-of-Use Asset, Amortization Expense</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6417,58 +6696,61 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>3811</v>
       </c>
       <c r="F38" t="n">
-        <v>82</v>
+        <v>3811</v>
       </c>
       <c r="G38" t="n">
-        <v>52</v>
+        <v>3933</v>
       </c>
       <c r="H38" t="n">
-        <v>26</v>
+        <v>3933</v>
       </c>
       <c r="I38" t="n">
-        <v>73</v>
+        <v>3933</v>
       </c>
       <c r="J38" t="n">
-        <v>48</v>
+        <v>4835</v>
       </c>
       <c r="K38" t="n">
-        <v>24</v>
+        <v>4835</v>
       </c>
       <c r="L38" t="n">
-        <v>63</v>
+        <v>4835</v>
       </c>
       <c r="M38" t="n">
-        <v>40</v>
+        <v>2535</v>
       </c>
       <c r="N38" t="n">
-        <v>19</v>
+        <v>2535</v>
       </c>
       <c r="O38" t="n">
-        <v>40</v>
+        <v>2535</v>
       </c>
       <c r="P38" t="n">
-        <v>25</v>
+        <v>1595</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>1595</v>
       </c>
       <c r="R38" t="n">
-        <v>31</v>
+        <v>1595</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>1470</v>
       </c>
       <c r="T38" t="n">
-        <v>10</v>
+        <v>1470</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1470</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Due to Related Parties</t>
+          <t>Proceeds from Issuance of Commercial Paper</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6484,55 +6766,58 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>78</v>
+        <v>947</v>
       </c>
       <c r="G39" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>-137</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>-109</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>-42</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-42</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>-98</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>-26</v>
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Debt</t>
+          <t>Operating Lease, Right-of-Use Asset, Amortization Expense</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6548,55 +6833,58 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>-750</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-750</v>
+        <v>82</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L40" t="n">
-        <v>-312</v>
+        <v>24</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R40" t="n">
-        <v>-200</v>
+        <v>12</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="U40" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Right-of-Use Asset Obtained in Exchange for Operating Lease Liability</t>
+          <t>Increase (Decrease) in Due to Related Parties</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6612,55 +6900,58 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
+        <v>78</v>
+      </c>
+      <c r="H41" t="n">
+        <v>42</v>
+      </c>
+      <c r="I41" t="n">
         <v>53</v>
       </c>
-      <c r="H41" t="n">
-        <v>25</v>
-      </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
+        <v>-137</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-150</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-109</v>
+      </c>
+      <c r="M41" t="n">
+        <v>313</v>
+      </c>
+      <c r="N41" t="n">
+        <v>277</v>
+      </c>
+      <c r="O41" t="n">
         <v>121</v>
       </c>
-      <c r="J41" t="n">
-        <v>50</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>119</v>
-      </c>
-      <c r="M41" t="n">
-        <v>87</v>
-      </c>
-      <c r="N41" t="n">
-        <v>7</v>
-      </c>
-      <c r="O41" t="n">
-        <v>128</v>
-      </c>
       <c r="P41" t="n">
-        <v>77</v>
+        <v>-42</v>
       </c>
       <c r="Q41" t="n">
-        <v>58</v>
+        <v>-42</v>
       </c>
       <c r="R41" t="n">
-        <v>40</v>
+        <v>-38</v>
       </c>
       <c r="S41" t="n">
-        <v>30</v>
+        <v>-98</v>
       </c>
       <c r="T41" t="n">
-        <v>25</v>
+        <v>-21</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Cash and Cash Equivalents, at Carrying Value</t>
+          <t>Repayments of Debt</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6679,52 +6970,55 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>4113</v>
+        <v>-750</v>
       </c>
       <c r="H42" t="n">
-        <v>4190</v>
+        <v>-750</v>
       </c>
       <c r="I42" t="n">
-        <v>3561</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>3841</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>3825</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>3398</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>4964</v>
+        <v>-312</v>
       </c>
       <c r="N42" t="n">
-        <v>4740</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>2440</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2623</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1763</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1296</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1775</v>
+        <v>-200</v>
       </c>
       <c r="T42" t="n">
-        <v>1330</v>
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Amortization Of Inventory Fair Value Adjustment</t>
+          <t>Cash and Cash Equivalents, at Carrying Value</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6746,49 +7040,52 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>4113</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>4190</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>3561</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>3841</v>
       </c>
       <c r="L43" t="n">
-        <v>187</v>
+        <v>3825</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3398</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4964</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>4740</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2440</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2623</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1763</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1296</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1775</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Gain (Loss) on Disposition of Property Plant Equipment</t>
+          <t>Amortization Of Inventory Fair Value Adjustment</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6813,46 +7110,49 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>15</v>
+        <v>187</v>
       </c>
       <c r="N44" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Equity Securities, FV-NI, Gain (Loss)</t>
+          <t>Gain (Loss) on Disposition of Property Plant Equipment</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6877,46 +7177,49 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L45" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="N45" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="O45" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="P45" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>19</v>
+      </c>
+      <c r="R45" t="n">
         <v>8</v>
       </c>
-      <c r="Q45" t="n">
-        <v>8</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="U45" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Due from Related Parties</t>
+          <t>Equity Securities, FV-NI, Gain (Loss)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6941,46 +7244,49 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
         <v>-1</v>
       </c>
       <c r="M46" t="n">
-        <v>-1</v>
+        <v>57</v>
       </c>
       <c r="N46" t="n">
-        <v>-1</v>
+        <v>54</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R46" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Lines of Credit</t>
+          <t>Increase (Decrease) in Due from Related Parties</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -7008,100 +7314,173 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>991</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>991</v>
+        <v>-1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>Proceeds from Lines of Credit</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>991</v>
+      </c>
+      <c r="N48" t="n">
+        <v>991</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>200</v>
+      </c>
+      <c r="T48" t="n">
+        <v>200</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>Amortization of Debt Issuance Costs and Discounts</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
         <v>4</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q49" t="n">
         <v>3</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R49" t="n">
         <v>2</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S49" t="n">
         <v>12</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T49" t="n">
         <v>8</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U49" t="n">
         <v>4</v>
       </c>
     </row>
